--- a/IANSEO scraper v2/urls.xlsx
+++ b/IANSEO scraper v2/urls.xlsx
@@ -1,31 +1,227 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robog\Desktop\aab\big_boy_scraper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robog\Documents\GitHub\Archers-Against-Bigotry-Datahub-1\IANSEO scraper v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFE6026-5EA7-444B-8701-974383A2F753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C93DC1-7659-4640-9E13-701E419A3632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-4575" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=15718</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12133</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12000</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=19253</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6209</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=25496</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=5015</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=19468</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=10154</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=13090</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16941</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=21500</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=15802</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=18931</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=3559</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=5074</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=3173</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=3558</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=5073</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=21664</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=13623</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=15321</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=18776</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=19655</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=15322</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=19654</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12225</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=21321</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=14347</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=17850</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=14346</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=17534</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=15793</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12327</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=861</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=1322</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=2192</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=3214</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=4739</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6526</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=9399</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=19661</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=24747</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=237</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=1664</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=10163</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=17423</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=19294</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12079</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=5024</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6675</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=9921</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12833</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16414</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=24098</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=10376</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=23301</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=13476</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=13478</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=13186</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16881</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16880</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=21629</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=21628</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=19981</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=19455</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6456</t>
+  </si>
   <si>
     <t>https://www.ianseo.net/Details.php?toId=3215</t>
   </si>
@@ -46,6 +242,75 @@
   </si>
   <si>
     <t>https://www.ianseo.net/Details.php?toId=24749</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=20812</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12629</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16346</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=20790</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=20620</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=15948</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26511</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26330</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26759</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26329</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26470</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26549</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26766</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26186</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26675</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26328</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26603</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26182</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26183</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26327</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=25066</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26170</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26274</t>
   </si>
 </sst>
 </file>
@@ -88,7 +353,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -111,44 +376,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -175,15 +440,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -210,7 +474,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -222,186 +485,660 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A97"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/IANSEO scraper v2/urls.xlsx
+++ b/IANSEO scraper v2/urls.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C93DC1-7659-4640-9E13-701E419A3632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4575" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27660" yWindow="-3315" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/IANSEO scraper v2/urls.xlsx
+++ b/IANSEO scraper v2/urls.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robog\Documents\GitHub\Archers-Against-Bigotry-Datahub-1\IANSEO scraper v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C93DC1-7659-4640-9E13-701E419A3632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2307564-C40E-4890-895E-D0FB645E50F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27660" yWindow="-3315" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="11380" windowHeight="13370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>https://www.ianseo.net/Details.php?toId=15718</t>
   </si>
@@ -311,6 +311,66 @@
   </si>
   <si>
     <t>https://www.ianseo.net/Details.php?toId=26274</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=26685</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=24037</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=24322</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=25594</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=25621</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=25557</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=25456</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=25279</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=23223</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=23222</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=21665</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=21887</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=21946</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=20178</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=21631</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=20716</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=21358</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=21454</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=20889</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=20803</t>
   </si>
 </sst>
 </file>
@@ -650,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A97"/>
+  <dimension ref="A1:A117"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -1138,6 +1198,106 @@
         <v>96</v>
       </c>
     </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IANSEO scraper v2/urls.xlsx
+++ b/IANSEO scraper v2/urls.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robog\Documents\GitHub\Archers-Against-Bigotry-Datahub-1\IANSEO scraper v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2307564-C40E-4890-895E-D0FB645E50F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2071193B-FFE1-4A1C-83A8-FB340162CD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="11380" windowHeight="13370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="740" yWindow="730" windowWidth="16800" windowHeight="9680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
   <si>
     <t>https://www.ianseo.net/Details.php?toId=15718</t>
   </si>
@@ -371,16 +371,234 @@
   </si>
   <si>
     <t>https://www.ianseo.net/Details.php?toId=20803</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=20618</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=20130</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=20367</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=19866</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=18338</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=20029</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=17174</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=15801</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16871</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16878</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16605</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16682</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16680</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16741</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=15856</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16532</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16537</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=15998</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=16034</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=14805</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=15967</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=13521</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12940</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=13398</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12938</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12939</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12937</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12289</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12026</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=13003</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=12003</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=10377</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=10236</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=10374</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=10026</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=10027</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=10028</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=10040</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=9686</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=7058</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6816</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6963</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6812</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6813</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6738</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6948</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6814</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6470</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6457</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6381</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=6052</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=5355</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=5267</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=4914</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=5151</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=4915</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=5150</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=5066</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=4841</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=4770</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=3599</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=3731</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=3631</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=3656</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=3340</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=2546</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=2406</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=2085</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=929</t>
+  </si>
+  <si>
+    <t>https://www.ianseo.net/Details.php?toId=450</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -403,13 +621,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -710,7 +931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A117"/>
+  <dimension ref="A1:A187"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -1298,7 +1519,361 @@
         <v>116</v>
       </c>
     </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A121" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A126" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A121" r:id="rId1" xr:uid="{DBCB34F7-13D5-4887-88B5-E5F9AE2C5B29}"/>
+    <hyperlink ref="A126" r:id="rId2" xr:uid="{1DFC794B-7257-4F35-B5FD-4D3E043ECEDC}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>